--- a/pepfoundry/project/core/amino_acids_library.xlsx
+++ b/pepfoundry/project/core/amino_acids_library.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10824"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielgarzonotero/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD461F28-04B9-4140-8E19-B56BD42E18DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DB2F0C-1035-C346-8942-3E1C2AEA67EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Database" sheetId="9" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Database!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Database!$A$1:$K$155</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="136">
+  <futureMetadata name="XLRICHVALUE" count="154">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -996,8 +996,134 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="136"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="137"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="138"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="139"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="140"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="141"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="142"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="143"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="144"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="145"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="146"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="147"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="148"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="149"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="150"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="151"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="152"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="153"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="136">
+  <valueMetadata count="154">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -1405,13 +1531,67 @@
     </bk>
     <bk>
       <rc t="1" v="135"/>
+    </bk>
+    <bk>
+      <rc t="1" v="136"/>
+    </bk>
+    <bk>
+      <rc t="1" v="137"/>
+    </bk>
+    <bk>
+      <rc t="1" v="138"/>
+    </bk>
+    <bk>
+      <rc t="1" v="139"/>
+    </bk>
+    <bk>
+      <rc t="1" v="140"/>
+    </bk>
+    <bk>
+      <rc t="1" v="141"/>
+    </bk>
+    <bk>
+      <rc t="1" v="142"/>
+    </bk>
+    <bk>
+      <rc t="1" v="143"/>
+    </bk>
+    <bk>
+      <rc t="1" v="144"/>
+    </bk>
+    <bk>
+      <rc t="1" v="145"/>
+    </bk>
+    <bk>
+      <rc t="1" v="146"/>
+    </bk>
+    <bk>
+      <rc t="1" v="147"/>
+    </bk>
+    <bk>
+      <rc t="1" v="148"/>
+    </bk>
+    <bk>
+      <rc t="1" v="149"/>
+    </bk>
+    <bk>
+      <rc t="1" v="150"/>
+    </bk>
+    <bk>
+      <rc t="1" v="151"/>
+    </bk>
+    <bk>
+      <rc t="1" v="152"/>
+    </bk>
+    <bk>
+      <rc t="1" v="153"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="611">
   <si>
     <t>#</t>
   </si>
@@ -3799,7 +3979,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>C(=O)C[C@H](N)</t>
+      <t>[C@H](C(C)C)</t>
     </r>
     <r>
       <rPr>
@@ -3837,7 +4017,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>C(=O)C[C@@H](N)</t>
+      <t>[C@@H](C(C)C)</t>
     </r>
     <r>
       <rPr>
@@ -3875,7 +4055,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H](C(C)C)</t>
+      <t>C</t>
     </r>
     <r>
       <rPr>
@@ -3913,7 +4093,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H](C(C)C)</t>
+      <t>[C@H](CO)</t>
     </r>
     <r>
       <rPr>
@@ -3951,6 +4131,2937 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>[C@@H](CO)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCC(=O)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCC(=O)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1ccc(O)cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1ccc(O)cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC(=O)O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC(=O)O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCC(=O)O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCC(=O)O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](C(CO))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C(CO))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C)[C@@H](C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C)[C@H](C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CS(CNC(=O)C))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CS(CNC(=O)C))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1ccc(OC)cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1ccc(OC)cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1c(C)cc(O)cc(C)1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1c(C)cc(O)cc(C)1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](C(C1=CC2=CC=CC=C2C=C1))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C(C1=CC2=CC=CC=C2C=C1))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCNC(=O)CCCC[C@@H]1[C@@H]2NC(=O)N[C@@H]2CS1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=O)CCCC[C@H]1[C@H]2NC(=O)N[C@H]2CS1)[C@H](CCCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=O)CCCCCNC(=O)CCCC[C@H]1[C@H]2NC(=O)N[C@H]2CS1)[C@H](CCCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCNC(=O)C1=CC=C(C(=O)C2=CC=CC=C2)C=C1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=O)C1C=CC(C(=O)C2=CC=CC=C2)=CC=1)[C@H](CCCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1ccc([N]=[N+]=[N-])cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1ccc([N]=[N+]=[N-])cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C([N]=[N+]=[N-]))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCNC(=N)N([N+](=O)[O-]))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCN(C(=O)C))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1CCC[C@@H]1C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCCCNC(=N)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCNC(=N)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC(C)1N=N1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC(C)1N=N1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCC(C)1N=N1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=S)N(C1=CC=C(C2=C1C(=O)OC23C4=C(C=C(C=C4)O)OC5=C3C=CC(=C5)O)))CCCCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC1C=CC(C(=O)O)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC(C(=O)O)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC1C=CC(C)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC(C)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC=C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C(C1C=CC=CC=1)(C1C=CC=CC=1))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC=C(C)C=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC(C2C=CC=CC=2)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC(C(C)(C)(C))=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1CC(O)C[C@@H]1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>Exception</t>
+  </si>
+  <si>
+    <t>Just for the last position</t>
+  </si>
+  <si>
+    <t>D-Propargylglycine</t>
+  </si>
+  <si>
+    <t>{pra}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC#C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC#C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>[NH2]</t>
+  </si>
+  <si>
+    <t>71-00-1</t>
+  </si>
+  <si>
+    <t>351-50-8</t>
+  </si>
+  <si>
+    <t>74-79-3</t>
+  </si>
+  <si>
+    <t>157-06-2</t>
+  </si>
+  <si>
+    <t>56-87-1</t>
+  </si>
+  <si>
+    <t>923-27-3</t>
+  </si>
+  <si>
+    <t>73-32-5</t>
+  </si>
+  <si>
+    <t>319-78-8</t>
+  </si>
+  <si>
+    <t>63-91-2</t>
+  </si>
+  <si>
+    <t>673-06-3</t>
+  </si>
+  <si>
+    <t>61-90-5</t>
+  </si>
+  <si>
+    <t>328-38-1</t>
+  </si>
+  <si>
+    <t>54-12-6</t>
+  </si>
+  <si>
+    <t>153-94-6</t>
+  </si>
+  <si>
+    <t>56-41-7</t>
+  </si>
+  <si>
+    <t>338-69-2</t>
+  </si>
+  <si>
+    <t>63-68-3</t>
+  </si>
+  <si>
+    <t>348-67-4</t>
+  </si>
+  <si>
+    <t>147-85-3</t>
+  </si>
+  <si>
+    <t>344-25-2</t>
+  </si>
+  <si>
+    <t>52-90-4</t>
+  </si>
+  <si>
+    <t>921-01-7</t>
+  </si>
+  <si>
+    <t>70-47-3</t>
+  </si>
+  <si>
+    <t>2058-58-4</t>
+  </si>
+  <si>
+    <t>72-18-4</t>
+  </si>
+  <si>
+    <t>640-68-6</t>
+  </si>
+  <si>
+    <t>56-40-6</t>
+  </si>
+  <si>
+    <t>56-45-1</t>
+  </si>
+  <si>
+    <t>312-84-5</t>
+  </si>
+  <si>
+    <t>26700-71-0</t>
+  </si>
+  <si>
+    <t>5959-95-5</t>
+  </si>
+  <si>
+    <t>60-18-4</t>
+  </si>
+  <si>
+    <t>556-02-5</t>
+  </si>
+  <si>
+    <t>56-84-8</t>
+  </si>
+  <si>
+    <t>1783-96-6</t>
+  </si>
+  <si>
+    <t>56-86-0</t>
+  </si>
+  <si>
+    <t>6893-26-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>80-68-2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H]([C@@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>672-15-1</t>
+  </si>
+  <si>
+    <t>6027-21-0</t>
+  </si>
+  <si>
+    <t>3913-67-5</t>
+  </si>
+  <si>
+    <t>600-21-5</t>
+  </si>
+  <si>
+    <t>19647-70-2</t>
+  </si>
+  <si>
+    <t>168300-88-7</t>
+  </si>
+  <si>
+    <t>6230-11-1</t>
+  </si>
+  <si>
+    <t>201335-88-8</t>
+  </si>
+  <si>
+    <t>206060-54-0</t>
+  </si>
+  <si>
+    <t>136771-16-9</t>
+  </si>
+  <si>
+    <t>2812-28-4</t>
+  </si>
+  <si>
+    <t>2812-27-3</t>
+  </si>
+  <si>
+    <t>56-12-2</t>
+  </si>
+  <si>
+    <t>144-98-9</t>
+  </si>
+  <si>
+    <t>24830-94-2</t>
+  </si>
+  <si>
+    <t>76985-09-6</t>
+  </si>
+  <si>
+    <t>58438-03-2</t>
+  </si>
+  <si>
+    <t>741281-41-4</t>
+  </si>
+  <si>
+    <t>34670-43-4</t>
+  </si>
+  <si>
+    <t>1241681-80-0</t>
+  </si>
+  <si>
+    <t>1016163-79-3</t>
+  </si>
+  <si>
+    <t>1176270-25-9</t>
+  </si>
+  <si>
+    <t>Nα-Fmoc-Nδ-Azido-D-ornithine</t>
+  </si>
+  <si>
+    <t>50913-12-7</t>
+  </si>
+  <si>
+    <t>13594-51-9</t>
+  </si>
+  <si>
+    <t>156-86-5</t>
+  </si>
+  <si>
+    <t>1313054-60-2</t>
+  </si>
+  <si>
+    <t>2978-24-7</t>
+  </si>
+  <si>
+    <t>1360651-24-6</t>
+  </si>
+  <si>
+    <t>851960-68-4</t>
+  </si>
+  <si>
+    <t>L-Photo-Met</t>
+  </si>
+  <si>
+    <t>23235-01-0</t>
+  </si>
+  <si>
+    <t>220497-98-3</t>
+  </si>
+  <si>
+    <t>3326-32-7</t>
+  </si>
+  <si>
+    <t>4-Carboxy-L-phenylalanine</t>
+  </si>
+  <si>
+    <t>126109-42-0</t>
+  </si>
+  <si>
+    <t>4-Carboxy-D-phenylalanine</t>
+  </si>
+  <si>
+    <t>1991-87-3</t>
+  </si>
+  <si>
+    <t>49759-61-7</t>
+  </si>
+  <si>
+    <t>54594-06-8</t>
+  </si>
+  <si>
+    <t>149597-91-1</t>
+  </si>
+  <si>
+    <t>114926-39-5</t>
+  </si>
+  <si>
+    <t>170080-13-4</t>
+  </si>
+  <si>
+    <t>252049-14-2</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>{ac-P}</t>
+  </si>
+  <si>
+    <t>68-95-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[N:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=O)C)1CCC[C@H]1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>{gly-P}</t>
+  </si>
+  <si>
+    <t>N-Acetyl-L-Proline</t>
+  </si>
+  <si>
+    <t>Glycyl-L-Proline</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[N:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=O)CN)1CCC[C@H]1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>704-15-4</t>
+  </si>
+  <si>
+    <t>N-PEG4-L-Proline</t>
+  </si>
+  <si>
+    <t>{PEG4-P}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[N:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CCOCCOCCOCCOC(=O)O)1CCC[C@H]1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1CCC[C@H]1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+  </si>
+  <si>
+    <t>{P-am}</t>
+  </si>
+  <si>
+    <t>L-Prolinamide</t>
+  </si>
+  <si>
+    <t>7531-52-4</t>
+  </si>
+  <si>
+    <t>N-Acetyl-L-tryptophan</t>
+  </si>
+  <si>
+    <t>{ac-W}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=O)C)[C@@H](Cc1c[nH]c2ccccc12)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>1218-34-4</t>
+  </si>
+  <si>
+    <t>{o}</t>
+  </si>
+  <si>
+    <t>{O}</t>
+  </si>
+  <si>
+    <t>L-Pyrrolysine</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCCCNC(=O)C1C(C)CC=N1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>448235-52-7</t>
+  </si>
+  <si>
+    <t>D-Pyrrolysine</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCNC(=O)C1C(C)CC=N1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@@H](C)(CC))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H]([C@H](C)(CC))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCC(=O)O)</t>
+    </r>
+  </si>
+  <si>
+    <t>D-Ile-PEG4(CH2)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCCOCCOCCC(=O)O)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCCC(=O)O)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCC[N]=[N+]=[N-])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C)[C@@H]([C@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C)[C@H]([C@@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H]([C@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCN(=[N+]=[N-]))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCNC(N)=O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H]([C@@H](C)(CC))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>N-Histidine</t>
+  </si>
+  <si>
+    <t>{N-H}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CC=1NC=NC1)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of H</t>
+  </si>
+  <si>
+    <t>{N-R}</t>
+  </si>
+  <si>
+    <t>N-Arginine</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CCCNC(N)=N)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of R</t>
+  </si>
+  <si>
+    <t>{N-K}</t>
+  </si>
+  <si>
+    <t>{N-I}</t>
+  </si>
+  <si>
+    <t>{N-F}</t>
+  </si>
+  <si>
+    <t>{N-L}</t>
+  </si>
+  <si>
+    <t>{N-W}</t>
+  </si>
+  <si>
+    <t>{N-A}</t>
+  </si>
+  <si>
+    <t>{N-M}</t>
+  </si>
+  <si>
+    <t>{N-C}</t>
+  </si>
+  <si>
+    <t>{N-N}</t>
+  </si>
+  <si>
+    <t>{N-V}</t>
+  </si>
+  <si>
+    <t>{N-S}</t>
+  </si>
+  <si>
+    <t>{N-Q}</t>
+  </si>
+  <si>
+    <t>{N-Y}</t>
+  </si>
+  <si>
+    <t>{N-D}</t>
+  </si>
+  <si>
+    <t>{N-E}</t>
+  </si>
+  <si>
+    <t>{N-T}</t>
+  </si>
+  <si>
+    <t>N-Lysine</t>
+  </si>
+  <si>
+    <t>N-Isoleucine</t>
+  </si>
+  <si>
+    <t>N-Phenylalanine</t>
+  </si>
+  <si>
+    <t>N-Leucine</t>
+  </si>
+  <si>
+    <t>N-Tryptophan</t>
+  </si>
+  <si>
+    <t>N-Alanine</t>
+  </si>
+  <si>
+    <t>N-Methionine</t>
+  </si>
+  <si>
+    <t>N-Cysteine</t>
+  </si>
+  <si>
+    <t>N-Asparagine</t>
+  </si>
+  <si>
+    <t>N-Valine</t>
+  </si>
+  <si>
+    <t>N-Serine</t>
+  </si>
+  <si>
+    <t>N-Glutamine</t>
+  </si>
+  <si>
+    <t>N-Tyrosine</t>
+  </si>
+  <si>
+    <t>N-Aspartic Acid</t>
+  </si>
+  <si>
+    <t>N-Glutamic Acid</t>
+  </si>
+  <si>
+    <t>N-Threonine</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>(CCCCN)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>C</t>
     </r>
     <r>
@@ -3973,6 +7084,289 @@
     </r>
   </si>
   <si>
+    <t>N-substituted glycine analogue of L</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>([C@@H](C)(CC))C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>(Cc1ccccc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>(CC(C)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Cc1c[nH]c2ccccc12)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CCSC)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CS)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -3989,7 +7383,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H](CO)</t>
+      <t>[C@@H](CC(=O)N)</t>
     </r>
     <r>
       <rPr>
@@ -4027,7 +7421,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H](CO)</t>
+      <t>[C@H](CC(=O)N)</t>
     </r>
     <r>
       <rPr>
@@ -4055,7 +7449,7 @@
         <color theme="4"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>[NH2:1]</t>
+      <t>[NH1:1]</t>
     </r>
     <r>
       <rPr>
@@ -4065,7 +7459,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H](CCC(=O)N)</t>
+      <t>(CC(=O)N)C</t>
     </r>
     <r>
       <rPr>
@@ -4093,7 +7487,7 @@
         <color theme="4"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>[NH2:1]</t>
+      <t>[NH1:1]</t>
     </r>
     <r>
       <rPr>
@@ -4103,7 +7497,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H](CCC(=O)N)</t>
+      <t>(C(C)C)C</t>
     </r>
     <r>
       <rPr>
@@ -4131,7 +7525,7 @@
         <color theme="4"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>[NH2:1]</t>
+      <t>[NH1:1]</t>
     </r>
     <r>
       <rPr>
@@ -4141,7 +7535,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H](Cc1ccc(O)cc1)</t>
+      <t>(CO)C</t>
     </r>
     <r>
       <rPr>
@@ -4169,7 +7563,7 @@
         <color theme="4"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>[NH2:1]</t>
+      <t>[NH1:1]</t>
     </r>
     <r>
       <rPr>
@@ -4179,7 +7573,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H](Cc1ccc(O)cc1)</t>
+      <t>(CCC(=O)N)C</t>
     </r>
     <r>
       <rPr>
@@ -4207,7 +7601,7 @@
         <color theme="4"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>[NH2:1]</t>
+      <t>[NH1:1]</t>
     </r>
     <r>
       <rPr>
@@ -4217,7 +7611,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H](CC(=O)O)</t>
+      <t>(Cc1ccc(O)cc1)C</t>
     </r>
     <r>
       <rPr>
@@ -4245,7 +7639,7 @@
         <color theme="4"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>[NH2:1]</t>
+      <t>[NH1:1]</t>
     </r>
     <r>
       <rPr>
@@ -4255,7 +7649,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H](CC(=O)O)</t>
+      <t>(CC(=O)O)C</t>
     </r>
     <r>
       <rPr>
@@ -4283,7 +7677,7 @@
         <color theme="4"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>[NH2:1]</t>
+      <t>[NH1:1]</t>
     </r>
     <r>
       <rPr>
@@ -4293,7 +7687,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H](CCC(=O)O)</t>
+      <t>(CCC(=O)O)C</t>
     </r>
     <r>
       <rPr>
@@ -4321,7 +7715,7 @@
         <color theme="4"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>[NH2:1]</t>
+      <t>[NH1:1]</t>
     </r>
     <r>
       <rPr>
@@ -4331,7 +7725,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H](CCC(=O)O)</t>
+      <t>([C@H](O)C)C</t>
     </r>
     <r>
       <rPr>
@@ -4353,2414 +7747,86 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](C(CO))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C(CO))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C)[C@@H](C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C)[C@H](C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CS(CNC(=O)C))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CS(CNC(=O)C))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](Cc1ccc(OC)cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](Cc1ccc(OC)cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](Cc1c(C)cc(O)cc(C)1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](Cc1c(C)cc(O)cc(C)1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CCC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](C(C1=CC2=CC=CC=C2C=C1))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C(C1=CC2=CC=CC=C2C=C1))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCNC(=O)CCCC[C@@H]1[C@@H]2NC(=O)N[C@@H]2CS1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)CCCC[C@H]1[C@H]2NC(=O)N[C@H]2CS1)[C@H](CCCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)CCCCCNC(=O)CCCC[C@H]1[C@H]2NC(=O)N[C@H]2CS1)[C@H](CCCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCNC(=O)C1=CC=C(C(=O)C2=CC=CC=C2)C=C1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)C1C=CC(C(=O)C2=CC=CC=C2)=CC=1)[C@H](CCCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](Cc1ccc([N]=[N+]=[N-])cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](Cc1ccc([N]=[N+]=[N-])cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C([N]=[N+]=[N-]))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCNC(=N)N([N+](=O)[O-]))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCN(C(=O)C))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1CCC[C@@H]1C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCCCNC(=N)N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCNC(=N)N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC(C)1N=N1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC(C)1N=N1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCC(C)1N=N1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=S)N(C1=CC=C(C2=C1C(=O)OC23C4=C(C=C(C=C4)O)OC5=C3C=CC(=C5)O)))CCCCC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC1C=CC(C(=O)O)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC(C(=O)O)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC1C=CC(C)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC(C)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC=C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C(C1C=CC=CC=1)(C1C=CC=CC=1))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC=C(C)C=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC(C2C=CC=CC=2)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC(C(C)(C)(C))=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1CC(O)C[C@@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>Exception</t>
-  </si>
-  <si>
-    <t>Just for the last position</t>
-  </si>
-  <si>
-    <t>D-Propargylglycine</t>
-  </si>
-  <si>
-    <t>{pra}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC#C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC#C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>[NH2]</t>
-  </si>
-  <si>
-    <t>71-00-1</t>
-  </si>
-  <si>
-    <t>351-50-8</t>
-  </si>
-  <si>
-    <t>74-79-3</t>
-  </si>
-  <si>
-    <t>157-06-2</t>
-  </si>
-  <si>
-    <t>56-87-1</t>
-  </si>
-  <si>
-    <t>923-27-3</t>
-  </si>
-  <si>
-    <t>73-32-5</t>
-  </si>
-  <si>
-    <t>319-78-8</t>
-  </si>
-  <si>
-    <t>63-91-2</t>
-  </si>
-  <si>
-    <t>673-06-3</t>
-  </si>
-  <si>
-    <t>61-90-5</t>
-  </si>
-  <si>
-    <t>328-38-1</t>
-  </si>
-  <si>
-    <t>54-12-6</t>
-  </si>
-  <si>
-    <t>153-94-6</t>
-  </si>
-  <si>
-    <t>56-41-7</t>
-  </si>
-  <si>
-    <t>338-69-2</t>
-  </si>
-  <si>
-    <t>63-68-3</t>
-  </si>
-  <si>
-    <t>348-67-4</t>
-  </si>
-  <si>
-    <t>147-85-3</t>
-  </si>
-  <si>
-    <t>344-25-2</t>
-  </si>
-  <si>
-    <t>52-90-4</t>
-  </si>
-  <si>
-    <t>921-01-7</t>
-  </si>
-  <si>
-    <t>70-47-3</t>
-  </si>
-  <si>
-    <t>2058-58-4</t>
-  </si>
-  <si>
-    <t>72-18-4</t>
-  </si>
-  <si>
-    <t>640-68-6</t>
-  </si>
-  <si>
-    <t>56-40-6</t>
-  </si>
-  <si>
-    <t>56-45-1</t>
-  </si>
-  <si>
-    <t>312-84-5</t>
-  </si>
-  <si>
-    <t>26700-71-0</t>
-  </si>
-  <si>
-    <t>5959-95-5</t>
-  </si>
-  <si>
-    <t>60-18-4</t>
-  </si>
-  <si>
-    <t>556-02-5</t>
-  </si>
-  <si>
-    <t>56-84-8</t>
-  </si>
-  <si>
-    <t>1783-96-6</t>
-  </si>
-  <si>
-    <t>56-86-0</t>
-  </si>
-  <si>
-    <t>6893-26-1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>80-68-2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H]([C@@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>672-15-1</t>
-  </si>
-  <si>
-    <t>6027-21-0</t>
-  </si>
-  <si>
-    <t>3913-67-5</t>
-  </si>
-  <si>
-    <t>600-21-5</t>
-  </si>
-  <si>
-    <t>19647-70-2</t>
-  </si>
-  <si>
-    <t>168300-88-7</t>
-  </si>
-  <si>
-    <t>6230-11-1</t>
-  </si>
-  <si>
-    <t>201335-88-8</t>
-  </si>
-  <si>
-    <t>206060-54-0</t>
-  </si>
-  <si>
-    <t>136771-16-9</t>
-  </si>
-  <si>
-    <t>2812-28-4</t>
-  </si>
-  <si>
-    <t>2812-27-3</t>
-  </si>
-  <si>
-    <t>56-12-2</t>
-  </si>
-  <si>
-    <t>144-98-9</t>
-  </si>
-  <si>
-    <t>24830-94-2</t>
-  </si>
-  <si>
-    <t>76985-09-6</t>
-  </si>
-  <si>
-    <t>58438-03-2</t>
-  </si>
-  <si>
-    <t>741281-41-4</t>
-  </si>
-  <si>
-    <t>34670-43-4</t>
-  </si>
-  <si>
-    <t>1241681-80-0</t>
-  </si>
-  <si>
-    <t>1016163-79-3</t>
-  </si>
-  <si>
-    <t>1176270-25-9</t>
-  </si>
-  <si>
-    <t>Nα-Fmoc-Nδ-Azido-D-ornithine</t>
-  </si>
-  <si>
-    <t>50913-12-7</t>
-  </si>
-  <si>
-    <t>13594-51-9</t>
-  </si>
-  <si>
-    <t>156-86-5</t>
-  </si>
-  <si>
-    <t>1313054-60-2</t>
-  </si>
-  <si>
-    <t>2978-24-7</t>
-  </si>
-  <si>
-    <t>1360651-24-6</t>
-  </si>
-  <si>
-    <t>851960-68-4</t>
-  </si>
-  <si>
-    <t>L-Photo-Met</t>
-  </si>
-  <si>
-    <t>23235-01-0</t>
-  </si>
-  <si>
-    <t>220497-98-3</t>
-  </si>
-  <si>
-    <t>3326-32-7</t>
-  </si>
-  <si>
-    <t>4-Carboxy-L-phenylalanine</t>
-  </si>
-  <si>
-    <t>126109-42-0</t>
-  </si>
-  <si>
-    <t>4-Carboxy-D-phenylalanine</t>
-  </si>
-  <si>
-    <t>1991-87-3</t>
-  </si>
-  <si>
-    <t>49759-61-7</t>
-  </si>
-  <si>
-    <t>54594-06-8</t>
-  </si>
-  <si>
-    <t>149597-91-1</t>
-  </si>
-  <si>
-    <t>114926-39-5</t>
-  </si>
-  <si>
-    <t>170080-13-4</t>
-  </si>
-  <si>
-    <t>252049-14-2</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>{ac-P}</t>
-  </si>
-  <si>
-    <t>68-95-1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[N:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)C)1CCC[C@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>{gly-P}</t>
-  </si>
-  <si>
-    <t>N-Acetyl-L-Proline</t>
-  </si>
-  <si>
-    <t>Glycyl-L-Proline</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[N:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)CN)1CCC[C@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>704-15-4</t>
-  </si>
-  <si>
-    <t>N-PEG4-L-Proline</t>
-  </si>
-  <si>
-    <t>{PEG4-P}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[N:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CCOCCOCCOCCOC(=O)O)1CCC[C@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1CCC[C@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-  </si>
-  <si>
-    <t>{P-am}</t>
-  </si>
-  <si>
-    <t>L-Prolinamide</t>
-  </si>
-  <si>
-    <t>7531-52-4</t>
-  </si>
-  <si>
-    <t>N-Acetyl-L-tryptophan</t>
-  </si>
-  <si>
-    <t>{ac-W}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)C)[C@@H](Cc1c[nH]c2ccccc12)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>1218-34-4</t>
-  </si>
-  <si>
-    <t>{o}</t>
-  </si>
-  <si>
-    <t>{O}</t>
-  </si>
-  <si>
-    <t>L-Pyrrolysine</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCCCNC(=O)C1C(C)CC=N1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>448235-52-7</t>
-  </si>
-  <si>
-    <t>D-Pyrrolysine</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCNC(=O)C1C(C)CC=N1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@@H](C)(CC))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H]([C@H](C)(CC))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCC(=O)O)</t>
-    </r>
-  </si>
-  <si>
-    <t>D-Ile-PEG4(CH2)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCCOCCOCCC(=O)O)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCCC(=O)O)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCC[N]=[N+]=[N-])</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C)[C@@H]([C@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C)[C@H]([C@@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H]([C@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCN(=[N+]=[N-]))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCNC(N)=O)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H]([C@@H](C)(CC))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
+    <t>N-substituted glycine analogue of I</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of F</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of W</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of M</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of C</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of N</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of V</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of S</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of Q</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of Y</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of D</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of E</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of T</t>
+  </si>
+  <si>
+    <t>17136-36-6</t>
+  </si>
+  <si>
+    <t>3182-85-2</t>
+  </si>
+  <si>
+    <t>13113-08-1</t>
+  </si>
+  <si>
+    <t>107-97-1</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of A (Sarcosine)</t>
+  </si>
+  <si>
+    <t>34299-32-6</t>
+  </si>
+  <si>
+    <t>3183-21-9</t>
+  </si>
+  <si>
+    <t>15874-34-7</t>
+  </si>
+  <si>
+    <t>5657-08-9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -6866,6 +7932,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -6893,41 +7964,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6938,44 +8018,47 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6987,19 +8070,43 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7059,7 +8166,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="136">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="154">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -7602,6 +8709,78 @@
   </rv>
   <rv s="0">
     <v>135</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>136</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>137</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>138</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>139</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>140</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>141</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>142</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>143</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>144</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>145</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>146</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>147</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>148</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>149</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>150</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>151</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>152</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>153</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -7754,6 +8933,24 @@
   <rel r:id="rId134"/>
   <rel r:id="rId135"/>
   <rel r:id="rId136"/>
+  <rel r:id="rId137"/>
+  <rel r:id="rId138"/>
+  <rel r:id="rId139"/>
+  <rel r:id="rId140"/>
+  <rel r:id="rId141"/>
+  <rel r:id="rId142"/>
+  <rel r:id="rId143"/>
+  <rel r:id="rId144"/>
+  <rel r:id="rId145"/>
+  <rel r:id="rId146"/>
+  <rel r:id="rId147"/>
+  <rel r:id="rId148"/>
+  <rel r:id="rId149"/>
+  <rel r:id="rId150"/>
+  <rel r:id="rId151"/>
+  <rel r:id="rId152"/>
+  <rel r:id="rId153"/>
+  <rel r:id="rId154"/>
 </richValueRels>
 </file>
 
@@ -8054,7 +9251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD03261-8AC5-410F-A743-A6D54D43FB41}">
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K155"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.83203125" style="6" customWidth="1"/>
@@ -8103,7 +9300,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8129,7 +9326,7 @@
         <v>324</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I2" s="2" t="e" vm="1">
         <v>#VALUE!</v>
@@ -8158,7 +9355,7 @@
         <v>325</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I3" s="2" t="e" vm="2">
         <v>#VALUE!</v>
@@ -8187,7 +9384,7 @@
         <v>326</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I4" s="2" t="e" vm="3">
         <v>#VALUE!</v>
@@ -8216,7 +9413,7 @@
         <v>327</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I5" s="2" t="e" vm="4">
         <v>#VALUE!</v>
@@ -8245,7 +9442,7 @@
         <v>328</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I6" s="2" t="e" vm="5">
         <v>#VALUE!</v>
@@ -8274,7 +9471,7 @@
         <v>329</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I7" s="2" t="e" vm="6">
         <v>#VALUE!</v>
@@ -8300,10 +9497,10 @@
         <v>13</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="I8" s="2" t="e" vm="7">
         <v>#VALUE!</v>
@@ -8329,10 +9526,10 @@
         <v>16</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I9" s="2" t="e" vm="8">
         <v>#VALUE!</v>
@@ -8361,7 +9558,7 @@
         <v>330</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I10" s="2" t="e" vm="9">
         <v>#VALUE!</v>
@@ -8390,7 +9587,7 @@
         <v>331</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I11" s="2" t="e" vm="10">
         <v>#VALUE!</v>
@@ -8419,7 +9616,7 @@
         <v>332</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I12" s="2" t="e" vm="11">
         <v>#VALUE!</v>
@@ -8448,7 +9645,7 @@
         <v>333</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I13" s="2" t="e" vm="12">
         <v>#VALUE!</v>
@@ -8477,7 +9674,7 @@
         <v>335</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I14" s="2" t="e" vm="13">
         <v>#VALUE!</v>
@@ -8506,7 +9703,7 @@
         <v>334</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I15" s="2" t="e" vm="14">
         <v>#VALUE!</v>
@@ -8535,7 +9732,7 @@
         <v>336</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I16" s="2" t="e" vm="15">
         <v>#VALUE!</v>
@@ -8564,7 +9761,7 @@
         <v>337</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I17" s="2" t="e" vm="16">
         <v>#VALUE!</v>
@@ -8593,7 +9790,7 @@
         <v>338</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I18" s="2" t="e" vm="17">
         <v>#VALUE!</v>
@@ -8622,7 +9819,7 @@
         <v>339</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I19" s="2" t="e" vm="18">
         <v>#VALUE!</v>
@@ -8651,7 +9848,7 @@
         <v>340</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I20" s="2" t="e" vm="19">
         <v>#VALUE!</v>
@@ -8680,7 +9877,7 @@
         <v>341</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I21" s="2" t="e" vm="20">
         <v>#VALUE!</v>
@@ -8709,7 +9906,7 @@
         <v>342</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I22" s="2" t="e" vm="21">
         <v>#VALUE!</v>
@@ -8738,7 +9935,7 @@
         <v>343</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I23" s="2" t="e" vm="22">
         <v>#VALUE!</v>
@@ -8764,10 +9961,10 @@
         <v>13</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>344</v>
+        <v>579</v>
       </c>
       <c r="H24" s="27" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I24" s="2" t="e" vm="23">
         <v>#VALUE!</v>
@@ -8793,10 +9990,10 @@
         <v>16</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>345</v>
+        <v>580</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I25" s="2" t="e" vm="24">
         <v>#VALUE!</v>
@@ -8822,10 +10019,10 @@
         <v>13</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H26" s="27" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I26" s="2" t="e" vm="25">
         <v>#VALUE!</v>
@@ -8851,10 +10048,10 @@
         <v>16</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I27" s="2" t="e" vm="26">
         <v>#VALUE!</v>
@@ -8880,10 +10077,10 @@
         <v>13</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H28" s="27" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I28" s="2" t="e" vm="27">
         <v>#VALUE!</v>
@@ -8909,10 +10106,10 @@
         <v>13</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I29" s="2" t="e" vm="28">
         <v>#VALUE!</v>
@@ -8938,10 +10135,10 @@
         <v>16</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H30" s="27" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I30" s="2" t="e" vm="29">
         <v>#VALUE!</v>
@@ -8967,10 +10164,10 @@
         <v>13</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I31" s="2" t="e" vm="30">
         <v>#VALUE!</v>
@@ -8996,10 +10193,10 @@
         <v>16</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H32" s="27" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I32" s="2" t="e" vm="31">
         <v>#VALUE!</v>
@@ -9025,10 +10222,10 @@
         <v>13</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I33" s="2" t="e" vm="32">
         <v>#VALUE!</v>
@@ -9054,10 +10251,10 @@
         <v>16</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H34" s="27" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I34" s="2" t="e" vm="33">
         <v>#VALUE!</v>
@@ -9083,10 +10280,10 @@
         <v>13</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I35" s="2" t="e" vm="34">
         <v>#VALUE!</v>
@@ -9112,10 +10309,10 @@
         <v>16</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H36" s="27" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I36" s="2" t="e" vm="35">
         <v>#VALUE!</v>
@@ -9141,10 +10338,10 @@
         <v>13</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I37" s="2" t="e" vm="36">
         <v>#VALUE!</v>
@@ -9170,10 +10367,10 @@
         <v>16</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H38" s="27" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I38" s="2" t="e" vm="37">
         <v>#VALUE!</v>
@@ -9199,10 +10396,10 @@
         <v>13</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I39" s="2" t="e" vm="38">
         <v>#VALUE!</v>
@@ -9228,10 +10425,10 @@
         <v>16</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H40" s="27" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I40" s="2" t="e" vm="39">
         <v>#VALUE!</v>
@@ -9257,10 +10454,10 @@
         <v>13</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I41" s="2" t="e" vm="40">
         <v>#VALUE!</v>
@@ -9286,10 +10483,10 @@
         <v>16</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H42" s="27" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I42" s="2" t="e" vm="41">
         <v>#VALUE!</v>
@@ -9315,10 +10512,10 @@
         <v>13</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I43" s="2" t="e" vm="42">
         <v>#VALUE!</v>
@@ -9344,10 +10541,10 @@
         <v>16</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H44" s="27" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I44" s="2" t="e" vm="43">
         <v>#VALUE!</v>
@@ -9373,10 +10570,10 @@
         <v>13</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="I45" s="2" t="e" vm="44">
         <v>#VALUE!</v>
@@ -9402,10 +10599,10 @@
         <v>16</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H46" s="27" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I46" s="2" t="e" vm="45">
         <v>#VALUE!</v>
@@ -9431,10 +10628,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I47" s="2" t="e" vm="46">
         <v>#VALUE!</v>
@@ -9460,10 +10657,10 @@
         <v>16</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H48" s="27" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I48" s="2" t="e" vm="47">
         <v>#VALUE!</v>
@@ -9489,10 +10686,10 @@
         <v>13</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I49" s="2" t="e" vm="48">
         <v>#VALUE!</v>
@@ -9518,10 +10715,10 @@
         <v>16</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H50" s="27" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I50" s="2" t="e" vm="49">
         <v>#VALUE!</v>
@@ -9545,7 +10742,7 @@
         <v>112</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I51" s="2" t="e" vm="50">
         <v>#VALUE!</v>
@@ -9572,7 +10769,7 @@
         <v>115</v>
       </c>
       <c r="H52" s="27" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I52" s="2" t="e" vm="51">
         <v>#VALUE!</v>
@@ -9599,7 +10796,7 @@
         <v>118</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I53" s="2" t="e" vm="52">
         <v>#VALUE!</v>
@@ -9626,7 +10823,7 @@
         <v>121</v>
       </c>
       <c r="H54" s="27" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I54" s="2" t="e" vm="53">
         <v>#VALUE!</v>
@@ -9653,7 +10850,7 @@
         <v>124</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I55" s="2" t="e" vm="54">
         <v>#VALUE!</v>
@@ -9680,7 +10877,7 @@
         <v>127</v>
       </c>
       <c r="H56" s="27" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I56" s="2" t="e" vm="55">
         <v>#VALUE!</v>
@@ -9707,7 +10904,7 @@
         <v>129</v>
       </c>
       <c r="H57" s="28" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I57" s="2" t="e" vm="56">
         <v>#VALUE!</v>
@@ -9736,7 +10933,7 @@
         <v>13</v>
       </c>
       <c r="G58" s="36" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H58" s="28" t="s">
         <v>223</v>
@@ -9765,7 +10962,7 @@
         <v>133</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>16</v>
@@ -9911,7 +11108,7 @@
         <v>13</v>
       </c>
       <c r="G63" s="36" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H63" s="28" t="s">
         <v>223</v>
@@ -9946,7 +11143,7 @@
         <v>13</v>
       </c>
       <c r="G64" s="36" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H64" s="28" t="s">
         <v>223</v>
@@ -9981,7 +11178,7 @@
         <v>13</v>
       </c>
       <c r="G65" s="36" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H65" s="28" t="s">
         <v>223</v>
@@ -10016,10 +11213,10 @@
         <v>13</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H66" s="27" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I66" s="2" t="e" vm="65">
         <v>#VALUE!</v>
@@ -10045,10 +11242,10 @@
         <v>16</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I67" s="2" t="e" vm="66">
         <v>#VALUE!</v>
@@ -10074,10 +11271,10 @@
         <v>16</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H68" s="27" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I68" s="2" t="e" vm="67">
         <v>#VALUE!</v>
@@ -10103,10 +11300,10 @@
         <v>13</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I69" s="2" t="e" vm="68">
         <v>#VALUE!</v>
@@ -10132,10 +11329,10 @@
         <v>16</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H70" s="27" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I70" s="2" t="e" vm="69">
         <v>#VALUE!</v>
@@ -10161,10 +11358,10 @@
         <v>13</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H71" s="27" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I71" s="2" t="e" vm="70">
         <v>#VALUE!</v>
@@ -10190,10 +11387,10 @@
         <v>16</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H72" s="27" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I72" s="2" t="e" vm="71">
         <v>#VALUE!</v>
@@ -10219,7 +11416,7 @@
         <v>16</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H73" s="27" t="s">
         <v>223</v>
@@ -10248,7 +11445,7 @@
         <v>16</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H74" s="27" t="s">
         <v>223</v>
@@ -10277,10 +11474,10 @@
         <v>16</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H75" s="27" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I75" s="2" t="e" vm="74">
         <v>#VALUE!</v>
@@ -10306,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H76" s="27" t="s">
         <v>223</v>
@@ -10335,7 +11532,7 @@
         <v>16</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H77" s="27" t="s">
         <v>223</v>
@@ -10364,10 +11561,10 @@
         <v>13</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H78" s="27" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I78" s="2" t="e" vm="77">
         <v>#VALUE!</v>
@@ -10393,10 +11590,10 @@
         <v>16</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H79" s="27" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I79" s="2" t="e" vm="78">
         <v>#VALUE!</v>
@@ -10422,10 +11619,10 @@
         <v>16</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H80" s="27" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I80" s="2" t="e" vm="79">
         <v>#VALUE!</v>
@@ -10445,16 +11642,16 @@
         <v>175</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G81" s="34" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H81" s="27" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I81" s="2" t="e" vm="80">
         <v>#VALUE!</v>
@@ -10480,10 +11677,10 @@
         <v>16</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H82" s="27" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="I82" s="2" t="e" vm="81">
         <v>#VALUE!</v>
@@ -10507,7 +11704,7 @@
         <v>180</v>
       </c>
       <c r="H83" s="27" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I83" s="2" t="e" vm="82">
         <v>#VALUE!</v>
@@ -10536,7 +11733,7 @@
         <v>16</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H84" s="27" t="s">
         <v>223</v>
@@ -10565,10 +11762,10 @@
         <v>16</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H85" s="27" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I85" s="2" t="e" vm="84">
         <v>#VALUE!</v>
@@ -10594,10 +11791,10 @@
         <v>16</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H86" s="27" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I86" s="2" t="e" vm="85">
         <v>#VALUE!</v>
@@ -10623,10 +11820,10 @@
         <v>13</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H87" s="27" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="I87" s="2" t="e" vm="86">
         <v>#VALUE!</v>
@@ -10652,10 +11849,10 @@
         <v>16</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H88" s="27" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I88" s="2" t="e" vm="87">
         <v>#VALUE!</v>
@@ -10681,10 +11878,10 @@
         <v>16</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H89" s="27" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I89" s="2" t="e" vm="88">
         <v>#VALUE!</v>
@@ -10710,10 +11907,10 @@
         <v>13</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H90" s="27" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I90" s="2" t="e" vm="89">
         <v>#VALUE!</v>
@@ -10738,8 +11935,8 @@
       <c r="F91" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G91" s="18" t="s">
-        <v>387</v>
+      <c r="G91" s="37" t="s">
+        <v>385</v>
       </c>
       <c r="H91" s="27" t="s">
         <v>223</v>
@@ -10762,16 +11959,16 @@
         <v>197</v>
       </c>
       <c r="E92" s="25" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H92" s="27" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I92" s="2" t="e" vm="91">
         <v>#VALUE!</v>
@@ -10797,10 +11994,10 @@
         <v>13</v>
       </c>
       <c r="G93" s="23" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H93" s="27" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I93" s="2" t="e" vm="92">
         <v>#VALUE!</v>
@@ -10817,19 +12014,19 @@
         <v>319</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E94" s="22" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F94" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G94" s="24" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H94" s="27" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I94" s="2" t="e" vm="93">
         <v>#VALUE!</v>
@@ -10855,10 +12052,10 @@
         <v>13</v>
       </c>
       <c r="G95" s="24" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H95" s="27" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I95" s="2" t="e" vm="94">
         <v>#VALUE!</v>
@@ -10882,10 +12079,10 @@
         <v>204</v>
       </c>
       <c r="G96" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H96" s="27" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I96" s="2" t="e" vm="95">
         <v>#VALUE!</v>
@@ -10908,16 +12105,16 @@
         <v>205</v>
       </c>
       <c r="E97" s="25" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H97" s="27" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I97" s="2" t="e" vm="96">
         <v>#VALUE!</v>
@@ -10937,13 +12134,13 @@
         <v>206</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F98" s="25" t="s">
         <v>16</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H98" s="27" t="s">
         <v>223</v>
@@ -10972,10 +12169,10 @@
         <v>13</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I99" s="2" t="e" vm="98">
         <v>#VALUE!</v>
@@ -11001,10 +12198,10 @@
         <v>16</v>
       </c>
       <c r="G100" s="18" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I100" s="2" t="e" vm="99">
         <v>#VALUE!</v>
@@ -11030,10 +12227,10 @@
         <v>16</v>
       </c>
       <c r="G101" s="18" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I101" s="2" t="e" vm="100">
         <v>#VALUE!</v>
@@ -11059,10 +12256,10 @@
         <v>16</v>
       </c>
       <c r="G102" s="18" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I102" s="2" t="e" vm="101">
         <v>#VALUE!</v>
@@ -11088,10 +12285,10 @@
         <v>16</v>
       </c>
       <c r="G103" s="18" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H103" s="27" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I103" s="2" t="e" vm="102">
         <v>#VALUE!</v>
@@ -11117,10 +12314,10 @@
         <v>16</v>
       </c>
       <c r="G104" s="18" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H104" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="I104" s="2" t="e" vm="103">
         <v>#VALUE!</v>
@@ -11146,10 +12343,10 @@
         <v>16</v>
       </c>
       <c r="G105" s="18" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H105" s="27" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I105" s="2" t="e" vm="104">
         <v>#VALUE!</v>
@@ -11349,7 +12546,7 @@
         <v>16</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H112" s="27" t="s">
         <v>223</v>
@@ -11640,7 +12837,7 @@
         <v>16</v>
       </c>
       <c r="G122" s="34" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H122" s="27" t="s">
         <v>234</v>
@@ -11771,7 +12968,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="J126" s="21" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K126" s="2">
         <v>2</v>
@@ -11806,7 +13003,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="J127" s="21" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K127" s="2">
         <v>2</v>
@@ -11919,19 +13116,19 @@
         <v>319</v>
       </c>
       <c r="D131" s="29" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E131" s="29" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F131" s="29" t="s">
         <v>13</v>
       </c>
       <c r="G131" s="30" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H131" s="31" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I131" s="2" t="e" vm="130">
         <v>#VALUE!</v>
@@ -11954,19 +13151,19 @@
         <v>319</v>
       </c>
       <c r="D132" s="29" t="s">
+        <v>493</v>
+      </c>
+      <c r="E132" s="29" t="s">
         <v>495</v>
-      </c>
-      <c r="E132" s="29" t="s">
-        <v>497</v>
       </c>
       <c r="F132" s="29" t="s">
         <v>13</v>
       </c>
       <c r="G132" s="30" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H132" s="31" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I132" s="2" t="e" vm="131">
         <v>#VALUE!</v>
@@ -11989,16 +13186,16 @@
         <v>319</v>
       </c>
       <c r="D133" s="29" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E133" s="29" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F133" s="29" t="s">
         <v>13</v>
       </c>
       <c r="G133" s="30" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H133" s="31" t="s">
         <v>223</v>
@@ -12024,25 +13221,25 @@
         <v>319</v>
       </c>
       <c r="D134" s="29" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E134" s="29" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F134" s="29" t="s">
         <v>13</v>
       </c>
       <c r="G134" s="30" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H134" s="31" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I134" s="2" t="e" vm="133">
         <v>#VALUE!</v>
       </c>
       <c r="J134" s="32" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K134" s="2">
         <v>2</v>
@@ -12059,19 +13256,19 @@
         <v>319</v>
       </c>
       <c r="D135" s="29" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E135" s="29" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F135" s="29" t="s">
         <v>13</v>
       </c>
       <c r="G135" s="30" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H135" s="31" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I135" s="2" t="e" vm="134">
         <v>#VALUE!</v>
@@ -12088,19 +13285,19 @@
         <v>319</v>
       </c>
       <c r="D136" s="33" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E136" s="33" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F136" s="29" t="s">
         <v>13</v>
       </c>
       <c r="G136" s="34" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H136" s="35" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="I136" s="2" t="e" vm="135">
         <v>#VALUE!</v>
@@ -12117,16 +13314,16 @@
         <v>319</v>
       </c>
       <c r="D137" s="33" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E137" s="33" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F137" s="33" t="s">
         <v>16</v>
       </c>
       <c r="G137" s="34" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H137" s="35" t="s">
         <v>223</v>
@@ -12135,69 +13332,551 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="2"/>
-      <c r="B138" s="3"/>
-      <c r="C138" s="2"/>
-    </row>
-    <row r="139" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="2"/>
-      <c r="B139" s="3"/>
-      <c r="C139" s="2"/>
-    </row>
-    <row r="140" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="2"/>
-      <c r="B140" s="3"/>
-      <c r="C140" s="2"/>
-    </row>
-    <row r="141" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="2"/>
-      <c r="B141" s="3"/>
-      <c r="C141" s="2"/>
-    </row>
-    <row r="142" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="2"/>
-      <c r="B142" s="3"/>
-      <c r="C142" s="2"/>
-    </row>
-    <row r="143" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="2"/>
-      <c r="B143" s="3"/>
-      <c r="C143" s="2"/>
-    </row>
-    <row r="144" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="2"/>
-      <c r="B144" s="3"/>
-      <c r="C144" s="2"/>
-    </row>
-    <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="2"/>
-      <c r="B145" s="3"/>
-      <c r="C145" s="2"/>
-    </row>
-    <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="2"/>
-      <c r="B146" s="3"/>
-      <c r="C146" s="2"/>
-    </row>
-    <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="2"/>
-      <c r="B147" s="3"/>
-      <c r="C147" s="2"/>
-    </row>
-    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="2"/>
-      <c r="B148" s="3"/>
-      <c r="C148" s="2"/>
-    </row>
-    <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="2"/>
-      <c r="B149" s="3"/>
-      <c r="C149" s="2"/>
+    <row r="138" spans="1:11" s="43" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="38">
+        <v>137</v>
+      </c>
+      <c r="B138" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D138" s="44" t="s">
+        <v>531</v>
+      </c>
+      <c r="E138" s="44" t="s">
+        <v>530</v>
+      </c>
+      <c r="F138" s="41"/>
+      <c r="G138" s="42" t="s">
+        <v>532</v>
+      </c>
+      <c r="H138" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I138" s="38" t="e" vm="137">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J138" s="46" t="s">
+        <v>533</v>
+      </c>
+      <c r="K138" s="38"/>
+    </row>
+    <row r="139" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="2">
+        <v>138</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D139" s="47" t="s">
+        <v>534</v>
+      </c>
+      <c r="E139" s="47" t="s">
+        <v>535</v>
+      </c>
+      <c r="F139" s="33"/>
+      <c r="G139" s="37" t="s">
+        <v>536</v>
+      </c>
+      <c r="H139" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I139" s="2" t="e" vm="138">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J139" s="46" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" s="43" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="38">
+        <v>139</v>
+      </c>
+      <c r="B140" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C140" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="D140" s="44" t="s">
+        <v>538</v>
+      </c>
+      <c r="E140" s="41" t="s">
+        <v>554</v>
+      </c>
+      <c r="F140" s="41"/>
+      <c r="G140" s="42" t="s">
+        <v>570</v>
+      </c>
+      <c r="H140" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I140" s="38" t="e" vm="139">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J140" s="48" t="s">
+        <v>571</v>
+      </c>
+      <c r="K140" s="38"/>
+    </row>
+    <row r="141" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="2">
+        <v>140</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D141" s="47" t="s">
+        <v>539</v>
+      </c>
+      <c r="E141" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="F141" s="33"/>
+      <c r="G141" s="37" t="s">
+        <v>572</v>
+      </c>
+      <c r="H141" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I141" s="2" t="e" vm="140">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J141" s="46" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="2">
+        <v>141</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D142" s="47" t="s">
+        <v>540</v>
+      </c>
+      <c r="E142" s="33" t="s">
+        <v>556</v>
+      </c>
+      <c r="F142" s="33"/>
+      <c r="G142" s="37" t="s">
+        <v>573</v>
+      </c>
+      <c r="H142" s="45" t="s">
+        <v>602</v>
+      </c>
+      <c r="I142" s="2" t="e" vm="141">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J142" s="46" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="2">
+        <v>142</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D143" s="47" t="s">
+        <v>541</v>
+      </c>
+      <c r="E143" s="33" t="s">
+        <v>557</v>
+      </c>
+      <c r="F143" s="33"/>
+      <c r="G143" s="37" t="s">
+        <v>574</v>
+      </c>
+      <c r="H143" s="45" t="s">
+        <v>603</v>
+      </c>
+      <c r="I143" s="2" t="e" vm="142">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J143" s="46" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="2">
+        <v>143</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D144" s="47" t="s">
+        <v>542</v>
+      </c>
+      <c r="E144" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="F144" s="33"/>
+      <c r="G144" s="37" t="s">
+        <v>575</v>
+      </c>
+      <c r="H144" s="45" t="s">
+        <v>604</v>
+      </c>
+      <c r="I144" s="2" t="e" vm="143">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J144" s="46" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="2">
+        <v>144</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D145" s="47" t="s">
+        <v>543</v>
+      </c>
+      <c r="E145" s="33" t="s">
+        <v>559</v>
+      </c>
+      <c r="F145" s="33"/>
+      <c r="G145" s="37" t="s">
+        <v>576</v>
+      </c>
+      <c r="H145" s="45" t="s">
+        <v>605</v>
+      </c>
+      <c r="I145" s="2" t="e" vm="144">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J145" s="46" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="2">
+        <v>145</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D146" s="47" t="s">
+        <v>544</v>
+      </c>
+      <c r="E146" s="33" t="s">
+        <v>560</v>
+      </c>
+      <c r="F146" s="33"/>
+      <c r="G146" s="37" t="s">
+        <v>577</v>
+      </c>
+      <c r="H146" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I146" s="2" t="e" vm="145">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J146" s="46" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="2">
+        <v>147</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D147" s="47" t="s">
+        <v>545</v>
+      </c>
+      <c r="E147" s="33" t="s">
+        <v>561</v>
+      </c>
+      <c r="F147" s="33"/>
+      <c r="G147" s="37" t="s">
+        <v>578</v>
+      </c>
+      <c r="H147" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I147" s="2" t="e" vm="146">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J147" s="46" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="2">
+        <v>148</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D148" s="47" t="s">
+        <v>546</v>
+      </c>
+      <c r="E148" s="33" t="s">
+        <v>562</v>
+      </c>
+      <c r="F148" s="33"/>
+      <c r="G148" s="37" t="s">
+        <v>581</v>
+      </c>
+      <c r="H148" s="45" t="s">
+        <v>607</v>
+      </c>
+      <c r="I148" s="2" t="e" vm="147">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J148" s="46" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="2">
+        <v>149</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D149" s="47" t="s">
+        <v>547</v>
+      </c>
+      <c r="E149" s="33" t="s">
+        <v>563</v>
+      </c>
+      <c r="F149" s="33"/>
+      <c r="G149" s="37" t="s">
+        <v>582</v>
+      </c>
+      <c r="H149" s="45" t="s">
+        <v>608</v>
+      </c>
+      <c r="I149" s="2" t="e" vm="148">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J149" s="46" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="2">
+        <v>151</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D150" s="47" t="s">
+        <v>548</v>
+      </c>
+      <c r="E150" s="33" t="s">
+        <v>564</v>
+      </c>
+      <c r="F150" s="33"/>
+      <c r="G150" s="37" t="s">
+        <v>583</v>
+      </c>
+      <c r="H150" s="45" t="s">
+        <v>609</v>
+      </c>
+      <c r="I150" s="2" t="e" vm="149">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J150" s="46" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="2">
+        <v>152</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D151" s="47" t="s">
+        <v>549</v>
+      </c>
+      <c r="E151" s="33" t="s">
+        <v>565</v>
+      </c>
+      <c r="F151" s="33"/>
+      <c r="G151" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="H151" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I151" s="2" t="e" vm="150">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J151" s="46" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="2">
+        <v>153</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D152" s="47" t="s">
+        <v>550</v>
+      </c>
+      <c r="E152" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="F152" s="33"/>
+      <c r="G152" s="37" t="s">
+        <v>585</v>
+      </c>
+      <c r="H152" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I152" s="2" t="e" vm="151">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J152" s="46" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="2">
+        <v>154</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D153" s="47" t="s">
+        <v>551</v>
+      </c>
+      <c r="E153" s="33" t="s">
+        <v>567</v>
+      </c>
+      <c r="F153" s="33"/>
+      <c r="G153" s="37" t="s">
+        <v>586</v>
+      </c>
+      <c r="H153" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I153" s="2" t="e" vm="152">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J153" s="46" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="2">
+        <v>155</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D154" s="47" t="s">
+        <v>552</v>
+      </c>
+      <c r="E154" s="33" t="s">
+        <v>568</v>
+      </c>
+      <c r="F154" s="33"/>
+      <c r="G154" s="37" t="s">
+        <v>587</v>
+      </c>
+      <c r="H154" s="45" t="s">
+        <v>610</v>
+      </c>
+      <c r="I154" s="2" t="e" vm="153">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J154" s="46" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="2">
+        <v>156</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D155" s="47" t="s">
+        <v>553</v>
+      </c>
+      <c r="E155" s="33" t="s">
+        <v>569</v>
+      </c>
+      <c r="F155" s="33"/>
+      <c r="G155" s="37" t="s">
+        <v>588</v>
+      </c>
+      <c r="H155" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I155" s="2" t="e" vm="154">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J155" s="46" t="s">
+        <v>601</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{1AD03261-8AC5-410F-A743-A6D54D43FB41}"/>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <autoFilter ref="A1:K155" xr:uid="{1AD03261-8AC5-410F-A743-A6D54D43FB41}"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/pepfoundry/project/core/amino_acids_library.xlsx
+++ b/pepfoundry/project/core/amino_acids_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielgarzonotero/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DB2F0C-1035-C346-8942-3E1C2AEA67EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C583A4-B64E-2547-8728-5448FA6E1D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Database" sheetId="9" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Database!$A$1:$K$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Database!$A$1:$K$156</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="154">
+  <futureMetadata name="XLRICHVALUE" count="155">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1122,8 +1122,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="154"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="154">
+  <valueMetadata count="155">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -1585,13 +1592,16 @@
     </bk>
     <bk>
       <rc t="1" v="153"/>
+    </bk>
+    <bk>
+      <rc t="1" v="154"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="614">
   <si>
     <t>#</t>
   </si>
@@ -7038,13 +7048,16 @@
     <t>N-Threonine</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH:1]</t>
+    <t>N-substituted glycine analogue of L</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
     </r>
     <r>
       <rPr>
@@ -7052,6 +7065,732 @@
         <color theme="1"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
+      <t>([C@@H](C)(CC))C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>(Cc1ccccc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>(CC(C)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Cc1c[nH]c2ccccc12)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CCSC)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CS)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC(=O)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC(=O)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CC(=O)N)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(C)C)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CO)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CCC(=O)N)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Cc1ccc(O)cc1)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CC(=O)O)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CCC(=O)O)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>([C@H](O)C)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of I</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of F</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of W</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of M</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of C</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of N</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of V</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of S</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of Q</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of Y</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of D</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of E</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of T</t>
+  </si>
+  <si>
+    <t>17136-36-6</t>
+  </si>
+  <si>
+    <t>3182-85-2</t>
+  </si>
+  <si>
+    <t>13113-08-1</t>
+  </si>
+  <si>
+    <t>107-97-1</t>
+  </si>
+  <si>
+    <t>N-substituted glycine analogue of A (Sarcosine)</t>
+  </si>
+  <si>
+    <t>34299-32-6</t>
+  </si>
+  <si>
+    <t>3183-21-9</t>
+  </si>
+  <si>
+    <t>15874-34-7</t>
+  </si>
+  <si>
+    <t>5657-08-9</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
       <t>(CCCCN)</t>
     </r>
     <r>
@@ -7084,7 +7823,10 @@
     </r>
   </si>
   <si>
-    <t>N-substituted glycine analogue of L</t>
+    <t>{N-E-am}</t>
+  </si>
+  <si>
+    <t>N-Glutamide</t>
   </si>
   <si>
     <r>
@@ -7098,719 +7840,39 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>([C@H](O)C)C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>([C@@H](C)(CC))C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>(Cc1ccccc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>(CC(C)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Cc1c[nH]c2ccccc12)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CCSC)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CS)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC(=O)N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC(=O)N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CC(=O)N)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(C)C)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CO)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CCC(=O)N)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Cc1ccc(O)cc1)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CC(=O)O)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CCC(=O)O)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>([C@H](O)C)C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of I</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of F</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of W</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of M</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of C</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of N</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of V</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of S</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of Q</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of Y</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of D</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of E</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of T</t>
-  </si>
-  <si>
-    <t>17136-36-6</t>
-  </si>
-  <si>
-    <t>3182-85-2</t>
-  </si>
-  <si>
-    <t>13113-08-1</t>
-  </si>
-  <si>
-    <t>107-97-1</t>
-  </si>
-  <si>
-    <t>N-substituted glycine analogue of A (Sarcosine)</t>
-  </si>
-  <si>
-    <t>34299-32-6</t>
-  </si>
-  <si>
-    <t>3183-21-9</t>
-  </si>
-  <si>
-    <t>15874-34-7</t>
-  </si>
-  <si>
-    <t>5657-08-9</t>
+      <t>[NH2]</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8166,7 +8228,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="154">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="155">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -8781,6 +8843,10 @@
   </rv>
   <rv s="0">
     <v>153</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>154</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -8951,6 +9017,7 @@
   <rel r:id="rId152"/>
   <rel r:id="rId153"/>
   <rel r:id="rId154"/>
+  <rel r:id="rId155"/>
 </richValueRels>
 </file>
 
@@ -9251,7 +9318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD03261-8AC5-410F-A743-A6D54D43FB41}">
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.83203125" style="6" customWidth="1"/>
@@ -9961,7 +10028,7 @@
         <v>13</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H24" s="27" t="s">
         <v>427</v>
@@ -9990,7 +10057,7 @@
         <v>16</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H25" s="27" t="s">
         <v>428</v>
@@ -13411,7 +13478,7 @@
       </c>
       <c r="F140" s="41"/>
       <c r="G140" s="42" t="s">
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="H140" s="45" t="s">
         <v>223</v>
@@ -13420,7 +13487,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="J140" s="48" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K140" s="38"/>
     </row>
@@ -13442,7 +13509,7 @@
       </c>
       <c r="F141" s="33"/>
       <c r="G141" s="37" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H141" s="45" t="s">
         <v>223</v>
@@ -13451,7 +13518,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="J141" s="46" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
@@ -13472,16 +13539,16 @@
       </c>
       <c r="F142" s="33"/>
       <c r="G142" s="37" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H142" s="45" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="I142" s="2" t="e" vm="141">
         <v>#VALUE!</v>
       </c>
       <c r="J142" s="46" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
@@ -13502,16 +13569,16 @@
       </c>
       <c r="F143" s="33"/>
       <c r="G143" s="37" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H143" s="45" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I143" s="2" t="e" vm="142">
         <v>#VALUE!</v>
       </c>
       <c r="J143" s="46" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
@@ -13532,19 +13599,19 @@
       </c>
       <c r="F144" s="33"/>
       <c r="G144" s="37" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H144" s="45" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I144" s="2" t="e" vm="143">
         <v>#VALUE!</v>
       </c>
       <c r="J144" s="46" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -13562,19 +13629,19 @@
       </c>
       <c r="F145" s="33"/>
       <c r="G145" s="37" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H145" s="45" t="s">
+        <v>604</v>
+      </c>
+      <c r="I145" s="2" t="e" vm="144">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J145" s="46" t="s">
         <v>605</v>
       </c>
-      <c r="I145" s="2" t="e" vm="144">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J145" s="46" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="146" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -13592,7 +13659,7 @@
       </c>
       <c r="F146" s="33"/>
       <c r="G146" s="37" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H146" s="45" t="s">
         <v>223</v>
@@ -13601,10 +13668,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="J146" s="46" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>147</v>
       </c>
@@ -13622,7 +13689,7 @@
       </c>
       <c r="F147" s="33"/>
       <c r="G147" s="37" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H147" s="45" t="s">
         <v>223</v>
@@ -13631,10 +13698,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="J147" s="46" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -13652,19 +13719,19 @@
       </c>
       <c r="F148" s="33"/>
       <c r="G148" s="37" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H148" s="45" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I148" s="2" t="e" vm="147">
         <v>#VALUE!</v>
       </c>
       <c r="J148" s="46" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -13682,19 +13749,19 @@
       </c>
       <c r="F149" s="33"/>
       <c r="G149" s="37" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H149" s="45" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I149" s="2" t="e" vm="148">
         <v>#VALUE!</v>
       </c>
       <c r="J149" s="46" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>151</v>
       </c>
@@ -13712,19 +13779,19 @@
       </c>
       <c r="F150" s="33"/>
       <c r="G150" s="37" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H150" s="45" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I150" s="2" t="e" vm="149">
         <v>#VALUE!</v>
       </c>
       <c r="J150" s="46" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>152</v>
       </c>
@@ -13742,7 +13809,7 @@
       </c>
       <c r="F151" s="33"/>
       <c r="G151" s="37" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H151" s="45" t="s">
         <v>223</v>
@@ -13751,10 +13818,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="J151" s="46" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>153</v>
       </c>
@@ -13772,7 +13839,7 @@
       </c>
       <c r="F152" s="33"/>
       <c r="G152" s="37" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H152" s="45" t="s">
         <v>223</v>
@@ -13781,10 +13848,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="J152" s="46" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>154</v>
       </c>
@@ -13802,7 +13869,7 @@
       </c>
       <c r="F153" s="33"/>
       <c r="G153" s="37" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H153" s="45" t="s">
         <v>223</v>
@@ -13811,10 +13878,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="J153" s="46" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>155</v>
       </c>
@@ -13832,19 +13899,19 @@
       </c>
       <c r="F154" s="33"/>
       <c r="G154" s="37" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H154" s="45" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I154" s="2" t="e" vm="153">
         <v>#VALUE!</v>
       </c>
       <c r="J154" s="46" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>156</v>
       </c>
@@ -13862,7 +13929,7 @@
       </c>
       <c r="F155" s="33"/>
       <c r="G155" s="37" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H155" s="45" t="s">
         <v>223</v>
@@ -13871,11 +13938,42 @@
         <v>#VALUE!</v>
       </c>
       <c r="J155" s="46" t="s">
-        <v>601</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="2">
+        <v>157</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D156" s="47" t="s">
+        <v>611</v>
+      </c>
+      <c r="E156" s="47" t="s">
+        <v>612</v>
+      </c>
+      <c r="F156" s="33"/>
+      <c r="G156" s="37" t="s">
+        <v>613</v>
+      </c>
+      <c r="H156" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I156" s="2" t="e" vm="155">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J156" s="46"/>
+      <c r="K156" s="2">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K155" xr:uid="{1AD03261-8AC5-410F-A743-A6D54D43FB41}"/>
+  <autoFilter ref="A1:K156" xr:uid="{1AD03261-8AC5-410F-A743-A6D54D43FB41}"/>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/pepfoundry/project/core/amino_acids_library.xlsx
+++ b/pepfoundry/project/core/amino_acids_library.xlsx
@@ -6997,7 +6997,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7020,12 +7020,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -7103,22 +7097,22 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -7134,7 +7128,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7454,7 +7448,7 @@
     <col min="11" max="11" style="15" width="16.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7489,7 +7483,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -7520,7 +7514,7 @@
       <c r="J2" s="9"/>
       <c r="K2" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -7551,7 +7545,7 @@
       <c r="J3" s="9"/>
       <c r="K3" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -7582,7 +7576,7 @@
       <c r="J4" s="9"/>
       <c r="K4" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -7613,7 +7607,7 @@
       <c r="J5" s="9"/>
       <c r="K5" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -8512,7 +8506,7 @@
       <c r="J34" s="9"/>
       <c r="K34" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="104.25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -8543,7 +8537,7 @@
       <c r="J35" s="9"/>
       <c r="K35" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="104.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -8574,7 +8568,7 @@
       <c r="J36" s="9"/>
       <c r="K36" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="104.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -8605,7 +8599,7 @@
       <c r="J37" s="9"/>
       <c r="K37" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="104.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -11784,7 +11778,7 @@
       <c r="J138" s="14" t="s">
         <v>538</v>
       </c>
-      <c r="K138" s="5"/>
+      <c r="K138" s="10"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="104">
       <c r="A139" s="5">
@@ -11846,7 +11840,7 @@
       <c r="J140" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="K140" s="5"/>
+      <c r="K140" s="10"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="104">
       <c r="A141" s="5">

--- a/pepfoundry/project/core/amino_acids_library.xlsx
+++ b/pepfoundry/project/core/amino_acids_library.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielgarzonotero/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC822AC-8FF1-F341-A42C-28B42092C152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D8F0CA-3856-3448-B576-D8A339DB6E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1601,7 +1601,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="616">
   <si>
     <t>#</t>
   </si>
@@ -12863,6 +12863,12 @@
       <c r="I120" s="2" t="e" vm="119">
         <v>#VALUE!</v>
       </c>
+      <c r="J120" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="K120" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="121" spans="1:11" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
